--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,124 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09:29:37</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E3" t="n">
+        <v>245381</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9447</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="I3" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>364</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>331</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2470</v>
+      </c>
+      <c r="R3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>638</v>
+      </c>
+      <c r="T3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1026</v>
+      </c>
+      <c r="V3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,6 +820,124 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09:30:42</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>245100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9390</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I4" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>369</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>331</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1902</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2470</v>
+      </c>
+      <c r="R4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>647</v>
+      </c>
+      <c r="T4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1026</v>
+      </c>
+      <c r="V4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>4/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,124 @@
         </is>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09:31:58</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E5" t="n">
+        <v>245171</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9395</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I5" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>372</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>331</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2468</v>
+      </c>
+      <c r="R5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>642</v>
+      </c>
+      <c r="T5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="V5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,6 +1056,124 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09:33:02</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>245270</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9395</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="I6" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>367</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>331</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2455</v>
+      </c>
+      <c r="R6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>642</v>
+      </c>
+      <c r="T6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1011</v>
+      </c>
+      <c r="V6" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,6 +1174,124 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09:34:06</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>245585</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9395</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-338</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-331</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1493</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>650</v>
+      </c>
+      <c r="T7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>958</v>
+      </c>
+      <c r="V7" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mixed / no clear dominance</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1292,124 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09:35:11</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E8" t="n">
+        <v>245282</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9395</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="I8" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>376</v>
+      </c>
+      <c r="K8" t="n">
+        <v>347</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>346</v>
+      </c>
+      <c r="N8" t="n">
+        <v>346</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1912</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2417</v>
+      </c>
+      <c r="R8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>650</v>
+      </c>
+      <c r="T8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>958</v>
+      </c>
+      <c r="V8" t="n">
+        <v>41</v>
+      </c>
+      <c r="W8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,6 +1410,124 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>09:36:15</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="E9" t="n">
+        <v>245180</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9395</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="I9" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>376</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>346</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1881</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2401</v>
+      </c>
+      <c r="R9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>621</v>
+      </c>
+      <c r="T9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>958</v>
+      </c>
+      <c r="V9" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>3/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,6 +1528,224 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09:37:20</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E10" t="n">
+        <v>245045</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9368</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="I10" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>374</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>343</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1877</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2401</v>
+      </c>
+      <c r="R10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>619</v>
+      </c>
+      <c r="T10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>962</v>
+      </c>
+      <c r="V10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09:37:31</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="I11" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>374</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>343</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1847</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2401</v>
+      </c>
+      <c r="R11" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>619</v>
+      </c>
+      <c r="T11" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>962</v>
+      </c>
+      <c r="V11" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +1744,124 @@
         </is>
       </c>
       <c r="AI11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09:38:35</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E12" t="n">
+        <v>245155</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9367</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="I12" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>374</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>347</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1866</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2413</v>
+      </c>
+      <c r="R12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>638</v>
+      </c>
+      <c r="T12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>970</v>
+      </c>
+      <c r="V12" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +1862,124 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09:39:39</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E13" t="n">
+        <v>245060</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9367</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="I13" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>369</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>347</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1864</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2413</v>
+      </c>
+      <c r="R13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>638</v>
+      </c>
+      <c r="T13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>970</v>
+      </c>
+      <c r="V13" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,6 +1980,124 @@
         </is>
       </c>
       <c r="AI13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>09:40:44</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E14" t="n">
+        <v>245040</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9375</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="I14" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>368</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>364</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1844</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2430</v>
+      </c>
+      <c r="R14" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>619</v>
+      </c>
+      <c r="T14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>970</v>
+      </c>
+      <c r="V14" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2098,6 +2098,124 @@
         </is>
       </c>
       <c r="AI14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>09:41:48</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E15" t="n">
+        <v>245150</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9371</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="I15" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>368</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>364</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1838</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2430</v>
+      </c>
+      <c r="R15" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>613</v>
+      </c>
+      <c r="T15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>970</v>
+      </c>
+      <c r="V15" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,6 +2218,124 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>09:42:53</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="E16" t="n">
+        <v>245310</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9350</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="I16" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>374</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>368</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1837</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2442</v>
+      </c>
+      <c r="R16" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>608</v>
+      </c>
+      <c r="T16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>974</v>
+      </c>
+      <c r="V16" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2336,6 +2336,118 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09:46:07</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>252240</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4613</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I17" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>378</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>376</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1828</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2462</v>
+      </c>
+      <c r="R17" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>592</v>
+      </c>
+      <c r="T17" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>978</v>
+      </c>
+      <c r="V17" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2446,6 +2446,124 @@
         </is>
       </c>
       <c r="AI17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09:47:12</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E18" t="n">
+        <v>252188</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4614</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="I18" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>374</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>379</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1823</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2466</v>
+      </c>
+      <c r="R18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>591</v>
+      </c>
+      <c r="T18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>979</v>
+      </c>
+      <c r="V18" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2564,6 +2564,124 @@
         </is>
       </c>
       <c r="AI18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>09:48:17</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E19" t="n">
+        <v>252360</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4616</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I19" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>369</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>380</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1827</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2461</v>
+      </c>
+      <c r="R19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>600</v>
+      </c>
+      <c r="T19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>973</v>
+      </c>
+      <c r="V19" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,6 +2684,124 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>09:49:22</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>252460</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4617</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I20" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>367</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>379</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1824</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2457</v>
+      </c>
+      <c r="R20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>600</v>
+      </c>
+      <c r="T20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>970</v>
+      </c>
+      <c r="V20" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2800,6 +2800,124 @@
         </is>
       </c>
       <c r="AI20" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>09:50:26</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E21" t="n">
+        <v>252460</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4617</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="I21" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>367</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>380</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1832</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2460</v>
+      </c>
+      <c r="R21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>600</v>
+      </c>
+      <c r="T21" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>972</v>
+      </c>
+      <c r="V21" t="n">
+        <v>41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2918,6 +2918,124 @@
         </is>
       </c>
       <c r="AI21" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>09:53:38</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E22" t="n">
+        <v>252728</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4610</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="I22" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-338</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-380</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2253</v>
+      </c>
+      <c r="R22" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>604</v>
+      </c>
+      <c r="T22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>972</v>
+      </c>
+      <c r="V22" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,6 +3038,124 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>09:55:46</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E23" t="n">
+        <v>252728</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4617</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I23" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>29</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1388</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2261</v>
+      </c>
+      <c r="R23" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>602</v>
+      </c>
+      <c r="T23" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>969</v>
+      </c>
+      <c r="V23" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3156,6 +3156,124 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>09:56:51</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>252880</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4619</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I24" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>29</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1390</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2262</v>
+      </c>
+      <c r="R24" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>605</v>
+      </c>
+      <c r="T24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>969</v>
+      </c>
+      <c r="V24" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3274,6 +3274,124 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>09:57:55</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>252769</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4621</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I25" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>29</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1373</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2272</v>
+      </c>
+      <c r="R25" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>591</v>
+      </c>
+      <c r="T25" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>977</v>
+      </c>
+      <c r="V25" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3390,6 +3390,124 @@
         </is>
       </c>
       <c r="AI25" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>09:58:58</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E26" t="n">
+        <v>252753</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4622</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>29</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1368</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2281</v>
+      </c>
+      <c r="R26" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>591</v>
+      </c>
+      <c r="T26" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>985</v>
+      </c>
+      <c r="V26" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3508,6 +3508,124 @@
         </is>
       </c>
       <c r="AI26" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10:00:03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E27" t="n">
+        <v>252833</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4621</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I27" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>29</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1389</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2279</v>
+      </c>
+      <c r="R27" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>592</v>
+      </c>
+      <c r="T27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>982</v>
+      </c>
+      <c r="V27" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3628,6 +3628,124 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10:01:08</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E28" t="n">
+        <v>252710</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4619</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I28" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>29</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1387</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2281</v>
+      </c>
+      <c r="R28" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>592</v>
+      </c>
+      <c r="T28" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>983</v>
+      </c>
+      <c r="V28" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3744,6 +3744,124 @@
         </is>
       </c>
       <c r="AI28" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10:02:12</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E29" t="n">
+        <v>252523</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4623</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="I29" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1394</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2280</v>
+      </c>
+      <c r="R29" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>596</v>
+      </c>
+      <c r="T29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>981</v>
+      </c>
+      <c r="V29" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3862,6 +3862,124 @@
         </is>
       </c>
       <c r="AI29" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10:03:17</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E30" t="n">
+        <v>252555</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4627</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="I30" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>29</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1394</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2278</v>
+      </c>
+      <c r="R30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>596</v>
+      </c>
+      <c r="T30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>980</v>
+      </c>
+      <c r="V30" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3982,6 +3982,124 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10:05:25</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>252385</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4624</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I31" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>373</v>
+      </c>
+      <c r="K31" t="n">
+        <v>344</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>399</v>
+      </c>
+      <c r="N31" t="n">
+        <v>399</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1848</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2492</v>
+      </c>
+      <c r="R31" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>604</v>
+      </c>
+      <c r="T31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>971</v>
+      </c>
+      <c r="V31" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,6 +4098,124 @@
         </is>
       </c>
       <c r="AI31" t="inlineStr">
+        <is>
+          <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10:06:30</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>252400</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4623</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="I32" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>373</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>397</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1854</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2489</v>
+      </c>
+      <c r="R32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>607</v>
+      </c>
+      <c r="T32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U32" t="n">
+        <v>970</v>
+      </c>
+      <c r="V32" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
         <is>
           <t>1/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4218,6 +4218,124 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10:07:35</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>252385</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4625</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I33" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>29</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-344</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-397</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>608</v>
+      </c>
+      <c r="T33" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U33" t="n">
+        <v>969</v>
+      </c>
+      <c r="V33" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4336,6 +4336,124 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>2/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10:08:39</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E34" t="n">
+        <v>252543</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4625</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I34" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>29</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2276</v>
+      </c>
+      <c r="R34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>610</v>
+      </c>
+      <c r="T34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U34" t="n">
+        <v>970</v>
+      </c>
+      <c r="V34" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4454,6 +4454,124 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10:09:44</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>252657</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4625</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I35" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>29</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1402</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2276</v>
+      </c>
+      <c r="R35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S35" t="n">
+        <v>614</v>
+      </c>
+      <c r="T35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U35" t="n">
+        <v>971</v>
+      </c>
+      <c r="V35" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4572,6 +4572,124 @@
       <c r="AI35" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10:10:49</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E36" t="n">
+        <v>252491</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4624</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="I36" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>374</v>
+      </c>
+      <c r="K36" t="n">
+        <v>345</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>398</v>
+      </c>
+      <c r="N36" t="n">
+        <v>398</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1865</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2492</v>
+      </c>
+      <c r="R36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S36" t="n">
+        <v>614</v>
+      </c>
+      <c r="T36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U36" t="n">
+        <v>971</v>
+      </c>
+      <c r="V36" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI36"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4690,6 +4690,124 @@
       <c r="AI36" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10:11:54</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E37" t="n">
+        <v>252533</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="I37" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>374</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>398</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1863</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2492</v>
+      </c>
+      <c r="R37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>614</v>
+      </c>
+      <c r="T37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U37" t="n">
+        <v>971</v>
+      </c>
+      <c r="V37" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4808,6 +4808,124 @@
       <c r="AI37" t="inlineStr">
         <is>
           <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10:12:59</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E38" t="n">
+        <v>252533</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I38" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>29</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-345</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-398</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2275</v>
+      </c>
+      <c r="R38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>614</v>
+      </c>
+      <c r="T38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U38" t="n">
+        <v>971</v>
+      </c>
+      <c r="V38" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI38"/>
+  <dimension ref="A1:AI39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4926,6 +4926,124 @@
       <c r="AI38" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10:14:04</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E39" t="n">
+        <v>252524</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I39" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>29</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>614</v>
+      </c>
+      <c r="T39" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U39" t="n">
+        <v>971</v>
+      </c>
+      <c r="V39" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>2/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5044,6 +5044,124 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>2/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10:15:08</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E40" t="n">
+        <v>252539</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4631</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I40" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>29</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>615</v>
+      </c>
+      <c r="T40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>971</v>
+      </c>
+      <c r="V40" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5162,6 +5162,124 @@
       <c r="AI40" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10:16:13</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E41" t="n">
+        <v>252612</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4631</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I41" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J41" t="n">
+        <v>29</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>615</v>
+      </c>
+      <c r="T41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>971</v>
+      </c>
+      <c r="V41" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5278,6 +5278,124 @@
         </is>
       </c>
       <c r="AI41" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10:17:17</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E42" t="n">
+        <v>252620</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4629</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I42" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>29</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2275</v>
+      </c>
+      <c r="R42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S42" t="n">
+        <v>615</v>
+      </c>
+      <c r="T42" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U42" t="n">
+        <v>973</v>
+      </c>
+      <c r="V42" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>0/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5398,6 +5398,124 @@
       <c r="AI42" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10:18:22</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E43" t="n">
+        <v>252460</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4629</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="I43" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>374</v>
+      </c>
+      <c r="K43" t="n">
+        <v>345</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>398</v>
+      </c>
+      <c r="N43" t="n">
+        <v>398</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1864</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2493</v>
+      </c>
+      <c r="R43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S43" t="n">
+        <v>614</v>
+      </c>
+      <c r="T43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U43" t="n">
+        <v>973</v>
+      </c>
+      <c r="V43" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>0/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5516,6 +5516,124 @@
       <c r="AI43" t="inlineStr">
         <is>
           <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10:19:27</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>252396</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4629</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I44" t="n">
+        <v>245000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>372</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>398</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1852</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2494</v>
+      </c>
+      <c r="R44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>607</v>
+      </c>
+      <c r="T44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>974</v>
+      </c>
+      <c r="V44" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI44"/>
+  <dimension ref="A1:AI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5634,6 +5634,124 @@
       <c r="AI44" t="inlineStr">
         <is>
           <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10:20:32</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>252396</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4629</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="I45" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>29</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-343</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-398</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1386</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2291</v>
+      </c>
+      <c r="R45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>607</v>
+      </c>
+      <c r="T45" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>984</v>
+      </c>
+      <c r="V45" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>2/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI45"/>
+  <dimension ref="A1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5752,6 +5752,124 @@
       <c r="AI45" t="inlineStr">
         <is>
           <t>2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10:21:36</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>252532</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4628</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I46" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>29</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1390</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2284</v>
+      </c>
+      <c r="R46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>612</v>
+      </c>
+      <c r="T46" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U46" t="n">
+        <v>971</v>
+      </c>
+      <c r="V46" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI46"/>
+  <dimension ref="A1:AI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5870,6 +5870,124 @@
       <c r="AI46" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10:22:41</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E47" t="n">
+        <v>252570</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4627</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I47" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J47" t="n">
+        <v>29</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1389</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2282</v>
+      </c>
+      <c r="R47" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S47" t="n">
+        <v>612</v>
+      </c>
+      <c r="T47" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>971</v>
+      </c>
+      <c r="V47" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI47"/>
+  <dimension ref="A1:AI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5988,6 +5988,124 @@
       <c r="AI47" t="inlineStr">
         <is>
           <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10:23:46</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E48" t="n">
+        <v>252591</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4626</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="I48" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J48" t="n">
+        <v>29</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1392</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2278</v>
+      </c>
+      <c r="R48" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S48" t="n">
+        <v>613</v>
+      </c>
+      <c r="T48" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U48" t="n">
+        <v>968</v>
+      </c>
+      <c r="V48" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>1/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI48"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6106,6 +6106,124 @@
       <c r="AI48" t="inlineStr">
         <is>
           <t>1/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10:25:55</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E49" t="n">
+        <v>252591</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4626</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="I49" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J49" t="n">
+        <v>29</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1395</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2282</v>
+      </c>
+      <c r="R49" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S49" t="n">
+        <v>614</v>
+      </c>
+      <c r="T49" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U49" t="n">
+        <v>973</v>
+      </c>
+      <c r="V49" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6222,6 +6222,124 @@
         </is>
       </c>
       <c r="AI49" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10:27:00</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E50" t="n">
+        <v>252555</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I50" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J50" t="n">
+        <v>29</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1394</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R50" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S50" t="n">
+        <v>614</v>
+      </c>
+      <c r="T50" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U50" t="n">
+        <v>967</v>
+      </c>
+      <c r="V50" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AI51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6340,6 +6340,124 @@
         </is>
       </c>
       <c r="AI50" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10:29:09</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="E51" t="n">
+        <v>252555</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4630</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="I51" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J51" t="n">
+        <v>29</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2268</v>
+      </c>
+      <c r="R51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S51" t="n">
+        <v>616</v>
+      </c>
+      <c r="T51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U51" t="n">
+        <v>960</v>
+      </c>
+      <c r="V51" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI51"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6458,6 +6458,124 @@
         </is>
       </c>
       <c r="AI51" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10:30:14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E52" t="n">
+        <v>252500</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4631</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I52" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J52" t="n">
+        <v>29</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1399</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2272</v>
+      </c>
+      <c r="R52" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S52" t="n">
+        <v>616</v>
+      </c>
+      <c r="T52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U52" t="n">
+        <v>964</v>
+      </c>
+      <c r="V52" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6578,6 +6578,124 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10:32:23</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E53" t="n">
+        <v>252708</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4627</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I53" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J53" t="n">
+        <v>29</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S53" t="n">
+        <v>616</v>
+      </c>
+      <c r="T53" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U53" t="n">
+        <v>964</v>
+      </c>
+      <c r="V53" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:AI54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6696,6 +6696,124 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10:33:28</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E54" t="n">
+        <v>252670</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4632</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="I54" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J54" t="n">
+        <v>29</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1401</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2271</v>
+      </c>
+      <c r="R54" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>617</v>
+      </c>
+      <c r="T54" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U54" t="n">
+        <v>965</v>
+      </c>
+      <c r="V54" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W54" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI54"/>
+  <dimension ref="A1:AI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6814,6 +6814,124 @@
       <c r="AI54" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10:34:33</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E55" t="n">
+        <v>252750</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4632</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="I55" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J55" t="n">
+        <v>29</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2269</v>
+      </c>
+      <c r="R55" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S55" t="n">
+        <v>617</v>
+      </c>
+      <c r="T55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U55" t="n">
+        <v>963</v>
+      </c>
+      <c r="V55" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI55"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6930,6 +6930,124 @@
         </is>
       </c>
       <c r="AI55" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10:35:38</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E56" t="n">
+        <v>252840</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4634</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="I56" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J56" t="n">
+        <v>29</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1401</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2272</v>
+      </c>
+      <c r="R56" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S56" t="n">
+        <v>619</v>
+      </c>
+      <c r="T56" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U56" t="n">
+        <v>963</v>
+      </c>
+      <c r="V56" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7048,6 +7048,124 @@
         </is>
       </c>
       <c r="AI56" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10:37:46</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E57" t="n">
+        <v>252798</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4633</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I57" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J57" t="n">
+        <v>29</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R57" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S57" t="n">
+        <v>617</v>
+      </c>
+      <c r="T57" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U57" t="n">
+        <v>966</v>
+      </c>
+      <c r="V57" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W57" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7168,6 +7168,124 @@
       <c r="AI57" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10:38:51</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E58" t="n">
+        <v>252825</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4635</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I58" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J58" t="n">
+        <v>29</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2271</v>
+      </c>
+      <c r="R58" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S58" t="n">
+        <v>617</v>
+      </c>
+      <c r="T58" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U58" t="n">
+        <v>966</v>
+      </c>
+      <c r="V58" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W58" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7284,6 +7284,124 @@
         </is>
       </c>
       <c r="AI58" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10:41:00</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E59" t="n">
+        <v>252734</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4639</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I59" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J59" t="n">
+        <v>29</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2278</v>
+      </c>
+      <c r="R59" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S59" t="n">
+        <v>620</v>
+      </c>
+      <c r="T59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U59" t="n">
+        <v>969</v>
+      </c>
+      <c r="V59" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W59" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7402,6 +7402,124 @@
         </is>
       </c>
       <c r="AI59" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10:42:05</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E60" t="n">
+        <v>252833</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4639</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I60" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J60" t="n">
+        <v>29</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R60" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S60" t="n">
+        <v>620</v>
+      </c>
+      <c r="T60" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U60" t="n">
+        <v>961</v>
+      </c>
+      <c r="V60" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W60" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7520,6 +7520,124 @@
         </is>
       </c>
       <c r="AI60" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10:43:10</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E61" t="n">
+        <v>252800</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4640</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I61" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J61" t="n">
+        <v>29</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1396</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2269</v>
+      </c>
+      <c r="R61" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S61" t="n">
+        <v>619</v>
+      </c>
+      <c r="T61" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U61" t="n">
+        <v>959</v>
+      </c>
+      <c r="V61" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W61" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7640,6 +7640,124 @@
       <c r="AI61" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10:44:15</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="E62" t="n">
+        <v>252872</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4640</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I62" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J62" t="n">
+        <v>29</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1396</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2275</v>
+      </c>
+      <c r="R62" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S62" t="n">
+        <v>619</v>
+      </c>
+      <c r="T62" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U62" t="n">
+        <v>965</v>
+      </c>
+      <c r="V62" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W62" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7758,6 +7758,124 @@
       <c r="AI62" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10:45:19</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E63" t="n">
+        <v>252859</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4644</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="I63" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J63" t="n">
+        <v>29</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2257</v>
+      </c>
+      <c r="R63" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S63" t="n">
+        <v>619</v>
+      </c>
+      <c r="T63" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U63" t="n">
+        <v>947</v>
+      </c>
+      <c r="V63" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W63" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7874,6 +7874,124 @@
         </is>
       </c>
       <c r="AI63" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10:46:24</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E64" t="n">
+        <v>252958</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4646</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I64" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J64" t="n">
+        <v>29</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2257</v>
+      </c>
+      <c r="R64" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S64" t="n">
+        <v>618</v>
+      </c>
+      <c r="T64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U64" t="n">
+        <v>947</v>
+      </c>
+      <c r="V64" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W64" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7994,6 +7994,124 @@
       <c r="AI64" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10:47:28</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E65" t="n">
+        <v>253030</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4651</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="I65" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J65" t="n">
+        <v>29</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1404</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2236</v>
+      </c>
+      <c r="R65" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S65" t="n">
+        <v>623</v>
+      </c>
+      <c r="T65" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U65" t="n">
+        <v>943</v>
+      </c>
+      <c r="V65" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W65" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI65"/>
+  <dimension ref="A1:AI66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8110,6 +8110,124 @@
         </is>
       </c>
       <c r="AI65" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10:48:32</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E66" t="n">
+        <v>253029</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4647</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="I66" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J66" t="n">
+        <v>29</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1403</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R66" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S66" t="n">
+        <v>623</v>
+      </c>
+      <c r="T66" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U66" t="n">
+        <v>949</v>
+      </c>
+      <c r="V66" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W66" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI66"/>
+  <dimension ref="A1:AI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8228,6 +8228,124 @@
         </is>
       </c>
       <c r="AI66" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10:49:37</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>253029</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4648</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I67" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J67" t="n">
+        <v>29</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1398</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2254</v>
+      </c>
+      <c r="R67" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S67" t="n">
+        <v>618</v>
+      </c>
+      <c r="T67" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U67" t="n">
+        <v>949</v>
+      </c>
+      <c r="V67" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W67" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI67"/>
+  <dimension ref="A1:AI68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8348,6 +8348,124 @@
       <c r="AI67" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10:50:42</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E68" t="n">
+        <v>252920</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4647</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="I68" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J68" t="n">
+        <v>29</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2256</v>
+      </c>
+      <c r="R68" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S68" t="n">
+        <v>619</v>
+      </c>
+      <c r="T68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U68" t="n">
+        <v>948</v>
+      </c>
+      <c r="V68" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="W68" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>0/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI68"/>
+  <dimension ref="A1:AI69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8466,6 +8466,124 @@
       <c r="AI68" t="inlineStr">
         <is>
           <t>0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10:51:47</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E69" t="n">
+        <v>252758</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4649</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="I69" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J69" t="n">
+        <v>29</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1397</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2259</v>
+      </c>
+      <c r="R69" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S69" t="n">
+        <v>619</v>
+      </c>
+      <c r="T69" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U69" t="n">
+        <v>950</v>
+      </c>
+      <c r="V69" t="n">
+        <v>38</v>
+      </c>
+      <c r="W69" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI69"/>
+  <dimension ref="A1:AI70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8582,6 +8582,124 @@
         </is>
       </c>
       <c r="AI69" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10:52:51</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E70" t="n">
+        <v>252740</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4648</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="I70" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J70" t="n">
+        <v>29</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1396</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2257</v>
+      </c>
+      <c r="R70" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S70" t="n">
+        <v>619</v>
+      </c>
+      <c r="T70" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U70" t="n">
+        <v>948</v>
+      </c>
+      <c r="V70" t="n">
+        <v>38</v>
+      </c>
+      <c r="W70" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI70"/>
+  <dimension ref="A1:AI71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8702,6 +8702,124 @@
       <c r="AI70" t="inlineStr">
         <is>
           <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10:53:56</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E71" t="n">
+        <v>252925</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4652</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="I71" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J71" t="n">
+        <v>29</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1396</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2260</v>
+      </c>
+      <c r="R71" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S71" t="n">
+        <v>619</v>
+      </c>
+      <c r="T71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U71" t="n">
+        <v>949</v>
+      </c>
+      <c r="V71" t="n">
+        <v>38</v>
+      </c>
+      <c r="W71" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI71"/>
+  <dimension ref="A1:AI72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8820,124 @@
       <c r="AI71" t="inlineStr">
         <is>
           <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10:55:01</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="E72" t="n">
+        <v>252716</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4655</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I72" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J72" t="n">
+        <v>29</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1392</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2261</v>
+      </c>
+      <c r="R72" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S72" t="n">
+        <v>614</v>
+      </c>
+      <c r="T72" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U72" t="n">
+        <v>948</v>
+      </c>
+      <c r="V72" t="n">
+        <v>38</v>
+      </c>
+      <c r="W72" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI72"/>
+  <dimension ref="A1:AI73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8938,6 +8938,124 @@
       <c r="AI72" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10:56:06</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E73" t="n">
+        <v>252635</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4655</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I73" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J73" t="n">
+        <v>29</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1392</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2272</v>
+      </c>
+      <c r="R73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S73" t="n">
+        <v>614</v>
+      </c>
+      <c r="T73" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U73" t="n">
+        <v>958</v>
+      </c>
+      <c r="V73" t="n">
+        <v>38</v>
+      </c>
+      <c r="W73" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>2/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI73"/>
+  <dimension ref="A1:AI74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9054,6 +9054,124 @@
         </is>
       </c>
       <c r="AI73" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10:57:11</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E74" t="n">
+        <v>252615</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4655</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I74" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J74" t="n">
+        <v>29</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1393</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2271</v>
+      </c>
+      <c r="R74" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S74" t="n">
+        <v>615</v>
+      </c>
+      <c r="T74" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U74" t="n">
+        <v>958</v>
+      </c>
+      <c r="V74" t="n">
+        <v>38</v>
+      </c>
+      <c r="W74" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
         <is>
           <t>2/2</t>
         </is>

--- a/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
+++ b/backend/signal_logs/2026-08-24/index_tracker_SILVER_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI74"/>
+  <dimension ref="A1:AI75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9174,6 +9174,124 @@
       <c r="AI74" t="inlineStr">
         <is>
           <t>2/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>11:01:30</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="E75" t="n">
+        <v>252695</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4660</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="I75" t="n">
+        <v>246000</v>
+      </c>
+      <c r="J75" t="n">
+        <v>29</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1390</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2274</v>
+      </c>
+      <c r="R75" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S75" t="n">
+        <v>611</v>
+      </c>
+      <c r="T75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U75" t="n">
+        <v>955</v>
+      </c>
+      <c r="V75" t="n">
+        <v>38</v>
+      </c>
+      <c r="W75" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>245000</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>
